--- a/course-design-2/outputs/tables/ch6/19_skill_eda_scope_audit.xlsx
+++ b/course-design-2/outputs/tables/ch6/19_skill_eda_scope_audit.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_样本口径" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_主口径技能排名" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_扩展口径技能排名" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_具体技术技能" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_技术领域" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_业务能力" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_办公工具" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位类别技能画像" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_技能共现" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_技能薪资关联" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_双口径稳健性" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_办公工具去重校验" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="01_样本统计范围" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_主统计范围技能排名" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_扩展统计范围技能排名" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_具体技术技能" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_技术领域" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_业务能力" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_办公工具" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_岗位类别技能画像" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_技能共现" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_技能薪资关联" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_两种统计范围稳健性" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_办公工具去重校验" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -462,7 +462,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>口径内技能覆盖率</t>
+          <t>统计范围内技能覆盖率</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>论文正文主口径：企业明确提出的任职要求段落</t>
+          <t>论文正文主统计范围：企业明确提出的任职要求段落</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>扩展口径：未识别要求段落时使用模型安全 JD 全文，不丢弃岗位</t>
+          <t>扩展统计范围：未识别要求段落时使用模型安全 JD 全文，不丢弃岗位</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>独立缺失口径：无可用技能文本，禁止解释为「企业没有技能要求」</t>
+          <t>独立缺失统计范围：无可用技能文本，禁止解释为「企业没有技能要求」</t>
         </is>
       </c>
     </row>
@@ -659,7 +659,7 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>口径与措辞</t>
+          <t>统计范围与措辞</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
@@ -701,7 +701,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -768,7 +768,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -835,7 +835,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -902,7 +902,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -969,7 +969,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1103,7 +1103,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1170,7 +1170,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1237,7 +1237,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1304,7 +1304,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1371,7 +1371,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1438,7 +1438,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1505,7 +1505,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1572,7 +1572,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1639,7 +1639,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1706,7 +1706,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1773,7 +1773,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1840,7 +1840,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1907,7 +1907,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1974,7 +1974,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2041,7 +2041,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2108,7 +2108,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2242,7 +2242,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2309,7 +2309,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2376,7 +2376,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2443,7 +2443,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,7 +2510,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2577,7 +2577,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2644,7 +2644,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2711,7 +2711,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2778,7 +2778,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2845,7 +2845,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2912,7 +2912,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2979,7 +2979,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3046,7 +3046,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3113,7 +3113,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3180,7 +3180,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3247,7 +3247,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3314,7 +3314,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3381,7 +3381,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3448,7 +3448,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3515,7 +3515,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3582,7 +3582,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3649,7 +3649,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3716,7 +3716,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3783,7 +3783,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3840,7 +3840,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3897,7 +3897,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3954,7 +3954,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4011,7 +4011,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4068,7 +4068,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4125,7 +4125,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4182,7 +4182,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4239,7 +4239,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4296,7 +4296,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4353,7 +4353,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4410,7 +4410,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4467,7 +4467,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4524,7 +4524,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4638,7 +4638,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4695,7 +4695,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4752,7 +4752,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4809,7 +4809,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4866,7 +4866,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4923,7 +4923,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4980,7 +4980,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5037,7 +5037,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5094,7 +5094,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5151,7 +5151,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5208,7 +5208,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5265,7 +5265,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5322,7 +5322,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5379,7 +5379,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5436,7 +5436,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5493,7 +5493,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5550,7 +5550,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5607,7 +5607,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5664,7 +5664,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5778,7 +5778,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5835,7 +5835,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5892,7 +5892,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5949,7 +5949,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6006,7 +6006,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6063,7 +6063,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>扩展口径：技能数量档 × 薪资中点</t>
+          <t>扩展统计范围：技能数量档 × 薪资中点</t>
         </is>
       </c>
       <c r="B88" t="inlineStr"/>
@@ -6110,7 +6110,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>扩展口径：技能数量档 × 薪资中点</t>
+          <t>扩展统计范围：技能数量档 × 薪资中点</t>
         </is>
       </c>
       <c r="B89" t="inlineStr"/>
@@ -6157,7 +6157,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>扩展口径：技能数量档 × 薪资中点</t>
+          <t>扩展统计范围：技能数量档 × 薪资中点</t>
         </is>
       </c>
       <c r="B90" t="inlineStr"/>
@@ -6204,7 +6204,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>扩展口径：技能数量档 × 薪资中点</t>
+          <t>扩展统计范围：技能数量档 × 薪资中点</t>
         </is>
       </c>
       <c r="B91" t="inlineStr"/>
@@ -6251,7 +6251,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>扩展口径：技能数量档 × 薪资中点</t>
+          <t>扩展统计范围：技能数量档 × 薪资中点</t>
         </is>
       </c>
       <c r="B92" t="inlineStr"/>
@@ -6298,7 +6298,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>扩展口径：技能数量档 × 薪资中点</t>
+          <t>扩展统计范围：技能数量档 × 薪资中点</t>
         </is>
       </c>
       <c r="B93" t="inlineStr"/>
@@ -6374,12 +6374,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>主口径排名</t>
+          <t>主统计范围排名</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>扩展口径排名</t>
+          <t>扩展统计范围排名</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -6412,7 +6412,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6435,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6458,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6481,7 +6481,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6504,7 +6504,7 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6550,7 +6550,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6577,7 +6577,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6604,7 +6604,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6631,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6658,7 +6658,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6685,7 +6685,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6712,7 +6712,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6739,7 +6739,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6793,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6820,7 +6820,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6874,7 +6874,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6955,7 +6955,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7009,7 +7009,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7090,7 +7090,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7225,7 +7225,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7252,7 +7252,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7306,7 +7306,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7441,7 +7441,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7468,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7549,7 +7549,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7576,7 +7576,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7603,7 +7603,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7630,7 +7630,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7657,7 +7657,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7684,7 +7684,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7711,7 +7711,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7765,7 +7765,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7792,7 +7792,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7819,7 +7819,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7873,7 +7873,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7900,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
+          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>group = 办公工具，对 intern_id 去重后的岗位数（正式口径）</t>
+          <t>group = 办公工具，对 intern_id 去重后的岗位数（正式统计范围）</t>
         </is>
       </c>
     </row>
@@ -7968,7 +7968,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>组内技能岗位数简单相加（错误口径）</t>
+          <t>组内技能岗位数简单相加（错误统计范围）</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -17123,7 +17123,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>统计口径</t>
+          <t>统计范围</t>
         </is>
       </c>
     </row>
@@ -17170,7 +17170,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17311,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17358,7 +17358,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17405,7 +17405,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17452,7 +17452,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17499,7 +17499,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17546,7 +17546,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17593,7 +17593,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17687,7 +17687,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17781,7 +17781,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17828,7 +17828,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17875,7 +17875,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17922,7 +17922,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -17969,7 +17969,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18016,7 +18016,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>统计口径</t>
+          <t>统计范围</t>
         </is>
       </c>
     </row>
@@ -18181,7 +18181,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18275,7 +18275,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18416,7 +18416,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18463,7 +18463,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18510,7 +18510,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18557,7 +18557,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18604,7 +18604,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18651,7 +18651,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18698,7 +18698,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18745,7 +18745,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18792,7 +18792,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18839,7 +18839,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -18910,7 +18910,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>统计口径</t>
+          <t>统计范围</t>
         </is>
       </c>
     </row>
@@ -18957,7 +18957,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19004,7 +19004,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19051,7 +19051,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19098,7 +19098,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19192,7 +19192,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19239,7 +19239,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19310,7 +19310,7 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>统计口径</t>
+          <t>统计范围</t>
         </is>
       </c>
     </row>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19404,7 +19404,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19451,7 +19451,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>
@@ -19592,7 +19592,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
         </is>
       </c>
     </row>

--- a/course-design-2/outputs/tables/ch6/19_skill_eda_scope_audit.xlsx
+++ b/course-design-2/outputs/tables/ch6/19_skill_eda_scope_audit.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_样本统计范围" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_主统计范围技能排名" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_扩展统计范围技能排名" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_具体技术技能" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_技术领域" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_业务能力" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_办公工具" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_岗位类别技能画像" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_技能共现" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_技能薪资关联" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_两种统计范围稳健性" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_办公工具去重校验" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_样本统计范围" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_主统计范围技能排名" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_扩展统计范围技能排名" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_具体技术技能" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_技术领域" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_业务能力" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_办公工具" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_岗位类别技能画像" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_技能共现" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_技能薪资关联" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_两种统计范围稳健性" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_办公工具去重校验" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +491,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>论文正文主统计范围：企业明确提出的任职要求段落</t>
+          <t>论文正文主口径：企业明确提出的任职要求段落</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>扩展统计范围：未识别要求段落时使用模型安全 JD 全文，不丢弃岗位</t>
+          <t>扩展口径：未识别要求段落时使用模型安全 JD 全文，不丢弃岗位</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>独立缺失统计范围：无可用技能文本，禁止解释为「企业没有技能要求」</t>
+          <t>独立缺失口径：无可用技能文本，禁止解释为「企业没有技能要求」</t>
         </is>
       </c>
     </row>
@@ -701,7 +701,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -757,18 +757,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -824,18 +817,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -891,18 +877,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -958,18 +937,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1025,18 +997,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1092,18 +1057,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1159,18 +1117,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1226,18 +1177,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1293,18 +1237,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1360,18 +1297,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1427,18 +1357,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1494,18 +1417,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1561,18 +1477,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
-      <c r="W14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1628,18 +1537,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
-      <c r="W15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1695,18 +1597,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
-      <c r="W16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1762,18 +1657,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
-      <c r="W17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1829,18 +1717,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr"/>
-      <c r="W18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1896,18 +1777,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr"/>
-      <c r="W19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1963,18 +1837,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr"/>
-      <c r="W20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2030,18 +1897,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr"/>
-      <c r="W21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2097,18 +1957,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr"/>
-      <c r="W22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2164,18 +2017,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr"/>
-      <c r="W23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>主统计范围 REQUIREMENT_SECTION：逐技能有/无对比</t>
+          <t>主口径 REQUIREMENT_SECTION：逐技能有/无对比</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2231,18 +2077,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr"/>
-      <c r="W24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2298,18 +2137,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr"/>
-      <c r="W25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2365,18 +2197,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr"/>
-      <c r="W26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2432,18 +2257,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr"/>
-      <c r="W27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2499,18 +2317,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr"/>
-      <c r="W28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2566,18 +2377,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr"/>
-      <c r="W29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2633,18 +2437,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr"/>
-      <c r="W30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2700,18 +2497,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr"/>
-      <c r="W31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2767,18 +2557,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr"/>
-      <c r="W32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2834,18 +2617,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr"/>
-      <c r="W33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2901,18 +2677,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr"/>
-      <c r="W34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2968,18 +2737,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr"/>
-      <c r="W35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3035,18 +2797,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr"/>
-      <c r="W36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3102,18 +2857,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr"/>
-      <c r="W37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3169,18 +2917,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
-      <c r="W38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3236,18 +2977,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr"/>
-      <c r="W39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3303,18 +3037,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr"/>
-      <c r="W40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3370,18 +3097,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr"/>
-      <c r="W41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3437,18 +3157,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr"/>
-      <c r="W42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3504,18 +3217,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr"/>
-      <c r="W43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3571,18 +3277,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr"/>
-      <c r="W44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3638,18 +3337,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr"/>
-      <c r="W45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3705,18 +3397,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr"/>
-      <c r="W46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>扩展统计范围 ALL_USABLE：逐技能有/无对比（稳健性）</t>
+          <t>扩展口径 ALL_USABLE：逐技能有/无对比（稳健性）</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3772,18 +3457,11 @@
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr"/>
-      <c r="W47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3806,14 +3484,6 @@
       <c r="G48" t="n">
         <v>87.5</v>
       </c>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -3832,15 +3502,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr"/>
-      <c r="W48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3863,14 +3529,6 @@
       <c r="G49" t="n">
         <v>60</v>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -3889,15 +3547,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr"/>
-      <c r="W49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3920,14 +3574,6 @@
       <c r="G50" t="n">
         <v>50</v>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -3946,15 +3592,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr"/>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
-      <c r="W50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3977,14 +3619,6 @@
       <c r="G51" t="n">
         <v>50</v>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4003,15 +3637,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr"/>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr"/>
-      <c r="W51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4034,14 +3664,6 @@
       <c r="G52" t="n">
         <v>35</v>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4060,15 +3682,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr"/>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr"/>
-      <c r="W52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4091,14 +3709,6 @@
       <c r="G53" t="n">
         <v>0</v>
       </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4117,15 +3727,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr"/>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr"/>
-      <c r="W53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4148,14 +3754,6 @@
       <c r="G54" t="n">
         <v>0</v>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4174,15 +3772,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr"/>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr"/>
-      <c r="W54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4205,14 +3799,6 @@
       <c r="G55" t="n">
         <v>0</v>
       </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4231,15 +3817,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr"/>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr"/>
-      <c r="W55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4262,14 +3844,6 @@
       <c r="G56" t="n">
         <v>0</v>
       </c>
-      <c r="H56" t="inlineStr"/>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4288,15 +3862,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr"/>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr"/>
-      <c r="W56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4319,14 +3889,6 @@
       <c r="G57" t="n">
         <v>0</v>
       </c>
-      <c r="H57" t="inlineStr"/>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4345,15 +3907,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr"/>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr"/>
-      <c r="W57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4376,14 +3934,6 @@
       <c r="G58" t="n">
         <v>175</v>
       </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4402,15 +3952,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr"/>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4433,14 +3979,6 @@
       <c r="G59" t="n">
         <v>150</v>
       </c>
-      <c r="H59" t="inlineStr"/>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4459,15 +3997,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr"/>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4490,14 +4024,6 @@
       <c r="G60" t="n">
         <v>137.5</v>
       </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4516,15 +4042,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr"/>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4547,14 +4069,6 @@
       <c r="G61" t="n">
         <v>87.5</v>
       </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4573,15 +4087,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr"/>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4604,14 +4114,6 @@
       <c r="G62" t="n">
         <v>75</v>
       </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4630,15 +4132,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr"/>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4661,14 +4159,6 @@
       <c r="G63" t="n">
         <v>42.5</v>
       </c>
-      <c r="H63" t="inlineStr"/>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4687,15 +4177,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr"/>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4718,14 +4204,6 @@
       <c r="G64" t="n">
         <v>7.5</v>
       </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4744,15 +4222,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4775,14 +4249,6 @@
       <c r="G65" t="n">
         <v>0</v>
       </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4801,15 +4267,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4832,14 +4294,6 @@
       <c r="G66" t="n">
         <v>0</v>
       </c>
-      <c r="H66" t="inlineStr"/>
-      <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
-      <c r="K66" t="inlineStr"/>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
-      <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4858,15 +4312,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4889,14 +4339,6 @@
       <c r="G67" t="n">
         <v>0</v>
       </c>
-      <c r="H67" t="inlineStr"/>
-      <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4915,15 +4357,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr"/>
-      <c r="U67" t="inlineStr"/>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4946,14 +4384,6 @@
       <c r="G68" t="n">
         <v>175</v>
       </c>
-      <c r="H68" t="inlineStr"/>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -4972,15 +4402,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr"/>
-      <c r="U68" t="inlineStr"/>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5003,14 +4429,6 @@
       <c r="G69" t="n">
         <v>137.5</v>
       </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5029,15 +4447,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr"/>
-      <c r="U69" t="inlineStr"/>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5060,14 +4474,6 @@
       <c r="G70" t="n">
         <v>121</v>
       </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5086,15 +4492,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr"/>
-      <c r="U70" t="inlineStr"/>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5117,14 +4519,6 @@
       <c r="G71" t="n">
         <v>100</v>
       </c>
-      <c r="H71" t="inlineStr"/>
-      <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
-      <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5143,15 +4537,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr"/>
-      <c r="U71" t="inlineStr"/>
-      <c r="V71" t="inlineStr"/>
-      <c r="W71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5174,14 +4564,6 @@
       <c r="G72" t="n">
         <v>100</v>
       </c>
-      <c r="H72" t="inlineStr"/>
-      <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
-      <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5200,15 +4582,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T72" t="inlineStr"/>
-      <c r="U72" t="inlineStr"/>
-      <c r="V72" t="inlineStr"/>
-      <c r="W72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5231,14 +4609,6 @@
       <c r="G73" t="n">
         <v>75</v>
       </c>
-      <c r="H73" t="inlineStr"/>
-      <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5257,15 +4627,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T73" t="inlineStr"/>
-      <c r="U73" t="inlineStr"/>
-      <c r="V73" t="inlineStr"/>
-      <c r="W73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5288,14 +4654,6 @@
       <c r="G74" t="n">
         <v>60</v>
       </c>
-      <c r="H74" t="inlineStr"/>
-      <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5314,15 +4672,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
-      <c r="V74" t="inlineStr"/>
-      <c r="W74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5345,14 +4699,6 @@
       <c r="G75" t="n">
         <v>60</v>
       </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5371,15 +4717,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
-      <c r="V75" t="inlineStr"/>
-      <c r="W75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5402,14 +4744,6 @@
       <c r="G76" t="n">
         <v>60</v>
       </c>
-      <c r="H76" t="inlineStr"/>
-      <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5428,15 +4762,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr"/>
-      <c r="U76" t="inlineStr"/>
-      <c r="V76" t="inlineStr"/>
-      <c r="W76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5459,14 +4789,6 @@
       <c r="G77" t="n">
         <v>60</v>
       </c>
-      <c r="H77" t="inlineStr"/>
-      <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
-      <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5485,15 +4807,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr"/>
-      <c r="U77" t="inlineStr"/>
-      <c r="V77" t="inlineStr"/>
-      <c r="W77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5516,14 +4834,6 @@
       <c r="G78" t="n">
         <v>175</v>
       </c>
-      <c r="H78" t="inlineStr"/>
-      <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5542,15 +4852,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T78" t="inlineStr"/>
-      <c r="U78" t="inlineStr"/>
-      <c r="V78" t="inlineStr"/>
-      <c r="W78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5573,14 +4879,6 @@
       <c r="G79" t="n">
         <v>135</v>
       </c>
-      <c r="H79" t="inlineStr"/>
-      <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5599,15 +4897,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T79" t="inlineStr"/>
-      <c r="U79" t="inlineStr"/>
-      <c r="V79" t="inlineStr"/>
-      <c r="W79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5630,14 +4924,6 @@
       <c r="G80" t="n">
         <v>100</v>
       </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5656,15 +4942,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
-      <c r="V80" t="inlineStr"/>
-      <c r="W80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5687,14 +4969,6 @@
       <c r="G81" t="n">
         <v>100</v>
       </c>
-      <c r="H81" t="inlineStr"/>
-      <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5713,15 +4987,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
-      <c r="V81" t="inlineStr"/>
-      <c r="W81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5744,14 +5014,6 @@
       <c r="G82" t="n">
         <v>87.5</v>
       </c>
-      <c r="H82" t="inlineStr"/>
-      <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5770,15 +5032,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T82" t="inlineStr"/>
-      <c r="U82" t="inlineStr"/>
-      <c r="V82" t="inlineStr"/>
-      <c r="W82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5801,14 +5059,6 @@
       <c r="G83" t="n">
         <v>75</v>
       </c>
-      <c r="H83" t="inlineStr"/>
-      <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5827,15 +5077,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T83" t="inlineStr"/>
-      <c r="U83" t="inlineStr"/>
-      <c r="V83" t="inlineStr"/>
-      <c r="W83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5858,14 +5104,6 @@
       <c r="G84" t="n">
         <v>75</v>
       </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5884,15 +5122,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T84" t="inlineStr"/>
-      <c r="U84" t="inlineStr"/>
-      <c r="V84" t="inlineStr"/>
-      <c r="W84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5915,14 +5149,6 @@
       <c r="G85" t="n">
         <v>75</v>
       </c>
-      <c r="H85" t="inlineStr"/>
-      <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
-      <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5941,15 +5167,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T85" t="inlineStr"/>
-      <c r="U85" t="inlineStr"/>
-      <c r="V85" t="inlineStr"/>
-      <c r="W85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5972,14 +5194,6 @@
       <c r="G86" t="n">
         <v>75</v>
       </c>
-      <c r="H86" t="inlineStr"/>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -5998,15 +5212,11 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T86" t="inlineStr"/>
-      <c r="U86" t="inlineStr"/>
-      <c r="V86" t="inlineStr"/>
-      <c r="W86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>主统计范围 + 控制岗位细分类：细分类内部中位数差 Top5</t>
+          <t>主口径 + 控制岗位细分类：细分类内部中位数差 Top5</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6029,14 +5239,6 @@
       <c r="G87" t="n">
         <v>75</v>
       </c>
-      <c r="H87" t="inlineStr"/>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
-      <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -6055,38 +5257,18 @@
           <t>控制岗位类别结构差异后的描述性比较</t>
         </is>
       </c>
-      <c r="T87" t="inlineStr"/>
-      <c r="U87" t="inlineStr"/>
-      <c r="V87" t="inlineStr"/>
-      <c r="W87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>扩展统计范围：技能数量档 × 薪资中点</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr"/>
-      <c r="F88" t="inlineStr"/>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
-      <c r="I88" t="inlineStr"/>
-      <c r="J88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
-      <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
+          <t>扩展口径：技能数量档 × 薪资中点</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q88" t="inlineStr"/>
-      <c r="R88" t="inlineStr"/>
       <c r="S88" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -6110,30 +5292,14 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>扩展统计范围：技能数量档 × 薪资中点</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
-      <c r="C89" t="inlineStr"/>
-      <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
-      <c r="F89" t="inlineStr"/>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
-      <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
-      <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
+          <t>扩展口径：技能数量档 × 薪资中点</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q89" t="inlineStr"/>
-      <c r="R89" t="inlineStr"/>
       <c r="S89" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -6157,30 +5323,14 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>扩展统计范围：技能数量档 × 薪资中点</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
-      <c r="C90" t="inlineStr"/>
-      <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
+          <t>扩展口径：技能数量档 × 薪资中点</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q90" t="inlineStr"/>
-      <c r="R90" t="inlineStr"/>
       <c r="S90" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -6204,30 +5354,14 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>扩展统计范围：技能数量档 × 薪资中点</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
-      <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
+          <t>扩展口径：技能数量档 × 薪资中点</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q91" t="inlineStr"/>
-      <c r="R91" t="inlineStr"/>
       <c r="S91" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -6251,30 +5385,14 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>扩展统计范围：技能数量档 × 薪资中点</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr"/>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
-      <c r="F92" t="inlineStr"/>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
-      <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+          <t>扩展口径：技能数量档 × 薪资中点</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q92" t="inlineStr"/>
-      <c r="R92" t="inlineStr"/>
       <c r="S92" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -6298,30 +5416,14 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>扩展统计范围：技能数量档 × 薪资中点</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr"/>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
-      <c r="F93" t="inlineStr"/>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
-      <c r="I93" t="inlineStr"/>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr"/>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
-      <c r="N93" t="inlineStr"/>
-      <c r="O93" t="inlineStr"/>
+          <t>扩展口径：技能数量档 × 薪资中点</t>
+        </is>
+      </c>
       <c r="P93" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
         </is>
       </c>
-      <c r="Q93" t="inlineStr"/>
-      <c r="R93" t="inlineStr"/>
       <c r="S93" t="inlineStr">
         <is>
           <t>本表为描述性关联，禁止解读为因果；技能要求更多 ≠ 因果导致薪资更高</t>
@@ -6407,12 +5509,9 @@
       <c r="C2" t="n">
         <v>144</v>
       </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6430,12 +5529,9 @@
       <c r="C3" t="n">
         <v>8</v>
       </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6453,12 +5549,9 @@
       <c r="C4" t="n">
         <v>0.8</v>
       </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6476,12 +5569,9 @@
       <c r="C5" t="n">
         <v>17</v>
       </c>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6499,12 +5589,9 @@
       <c r="C6" t="n">
         <v>0.85</v>
       </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6522,12 +5609,9 @@
       <c r="C7" t="n">
         <v>0.973113</v>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6545,12 +5629,9 @@
       <c r="C8" t="n">
         <v>1.94934510245689e-92</v>
       </c>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>主统计范围 = REQUIREMENT_SECTION；扩展统计范围 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
+          <t>主口径 = REQUIREMENT_SECTION；扩展口径 = REQUIREMENT_SECTION + FULL_TEXT_FALLBACK；排名一致说明结论对文本结构识别方式稳健</t>
         </is>
       </c>
     </row>
@@ -6565,7 +5646,6 @@
           <t>数据分析</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="n">
         <v>1</v>
       </c>
@@ -6577,7 +5657,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6592,7 +5672,6 @@
           <t>Excel</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
       <c r="D10" t="n">
         <v>2</v>
       </c>
@@ -6604,7 +5683,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6619,7 +5698,6 @@
           <t>办公软件</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
       <c r="D11" t="n">
         <v>3</v>
       </c>
@@ -6631,7 +5709,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6646,7 +5724,6 @@
           <t>人工智能</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
       <c r="D12" t="n">
         <v>4</v>
       </c>
@@ -6658,7 +5735,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6673,7 +5750,6 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
       <c r="D13" t="n">
         <v>5</v>
       </c>
@@ -6685,7 +5761,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6700,7 +5776,6 @@
           <t>SQL</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
       <c r="D14" t="n">
         <v>6</v>
       </c>
@@ -6712,7 +5787,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6727,7 +5802,6 @@
           <t>PPT</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
       <c r="D15" t="n">
         <v>7</v>
       </c>
@@ -6739,7 +5813,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6754,7 +5828,6 @@
           <t>大模型</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
       <c r="D16" t="n">
         <v>8</v>
       </c>
@@ -6766,7 +5839,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6781,7 +5854,6 @@
           <t>Java</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
       <c r="D17" t="n">
         <v>9</v>
       </c>
@@ -6793,7 +5865,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6808,7 +5880,6 @@
           <t>C++</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="n">
         <v>10</v>
       </c>
@@ -6820,7 +5891,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6835,7 +5906,6 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="n">
         <v>11</v>
       </c>
@@ -6847,7 +5917,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6862,7 +5932,6 @@
           <t>机器学习</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="n">
         <v>12</v>
       </c>
@@ -6874,7 +5943,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6889,7 +5958,6 @@
           <t>内容运营</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="n">
         <v>13</v>
       </c>
@@ -6901,7 +5969,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6916,7 +5984,6 @@
           <t>深度学习</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="n">
         <v>14</v>
       </c>
@@ -6928,7 +5995,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6943,7 +6010,6 @@
           <t>C</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="n">
         <v>15</v>
       </c>
@@ -6955,7 +6021,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6036,6 @@
           <t>Linux</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="n">
         <v>16</v>
       </c>
@@ -6982,7 +6047,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -6997,7 +6062,6 @@
           <t>PyTorch</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="n">
         <v>17</v>
       </c>
@@ -7009,7 +6073,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7024,7 +6088,6 @@
           <t>原型设计</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
       <c r="D26" t="n">
         <v>18</v>
       </c>
@@ -7036,7 +6099,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7051,7 +6114,6 @@
           <t>项目管理</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
       <c r="D27" t="n">
         <v>19</v>
       </c>
@@ -7063,7 +6125,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7078,7 +6140,6 @@
           <t>数据可视化</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
       <c r="D28" t="n">
         <v>20</v>
       </c>
@@ -7090,7 +6151,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7105,7 +6166,6 @@
           <t>计算机视觉</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
       <c r="D29" t="n">
         <v>21</v>
       </c>
@@ -7117,7 +6177,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7132,7 +6192,6 @@
           <t>AIGC</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
       <c r="D30" t="n">
         <v>22</v>
       </c>
@@ -7144,7 +6203,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7159,7 +6218,6 @@
           <t>大数据</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
       <c r="D31" t="n">
         <v>23</v>
       </c>
@@ -7171,7 +6229,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7186,7 +6244,6 @@
           <t>TensorFlow</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
       <c r="D32" t="n">
         <v>24</v>
       </c>
@@ -7198,7 +6255,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7213,7 +6270,6 @@
           <t>产品设计</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
       <c r="D33" t="n">
         <v>25</v>
       </c>
@@ -7225,7 +6281,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7240,7 +6296,6 @@
           <t>MySQL</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr"/>
       <c r="D34" t="n">
         <v>26</v>
       </c>
@@ -7252,7 +6307,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7267,7 +6322,6 @@
           <t>JavaScript</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr"/>
       <c r="D35" t="n">
         <v>27</v>
       </c>
@@ -7279,7 +6333,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7294,7 +6348,6 @@
           <t>前端</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr"/>
       <c r="D36" t="n">
         <v>28</v>
       </c>
@@ -7306,7 +6359,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7321,7 +6374,6 @@
           <t>Git</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr"/>
       <c r="D37" t="n">
         <v>29</v>
       </c>
@@ -7333,7 +6385,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7348,7 +6400,6 @@
           <t>用户研究</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr"/>
       <c r="D38" t="n">
         <v>30</v>
       </c>
@@ -7360,7 +6411,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7375,7 +6426,6 @@
           <t>HTML</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr"/>
       <c r="D39" t="n">
         <v>31</v>
       </c>
@@ -7387,7 +6437,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7402,7 +6452,6 @@
           <t>后端</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
       <c r="D40" t="n">
         <v>32</v>
       </c>
@@ -7414,7 +6463,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7429,7 +6478,6 @@
           <t>NLP</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
       <c r="D41" t="n">
         <v>33</v>
       </c>
@@ -7441,7 +6489,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7456,7 +6504,6 @@
           <t>Prompt Engineering</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr"/>
       <c r="D42" t="n">
         <v>34</v>
       </c>
@@ -7468,7 +6515,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7483,7 +6530,6 @@
           <t>Tableau</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr"/>
       <c r="D43" t="n">
         <v>35</v>
       </c>
@@ -7495,7 +6541,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7510,7 +6556,6 @@
           <t>CSS</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr"/>
       <c r="D44" t="n">
         <v>36</v>
       </c>
@@ -7522,7 +6567,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7537,7 +6582,6 @@
           <t>Vue</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
       <c r="D45" t="n">
         <v>37</v>
       </c>
@@ -7549,7 +6593,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7564,7 +6608,6 @@
           <t>Agent</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
       <c r="D46" t="n">
         <v>38</v>
       </c>
@@ -7576,7 +6619,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7591,7 +6634,6 @@
           <t>多模态</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr"/>
       <c r="D47" t="n">
         <v>39</v>
       </c>
@@ -7603,7 +6645,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7618,7 +6660,6 @@
           <t>市场调研</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="n">
         <v>40</v>
       </c>
@@ -7630,7 +6671,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7645,7 +6686,6 @@
           <t>数据科学</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr"/>
       <c r="D49" t="n">
         <v>41</v>
       </c>
@@ -7657,7 +6697,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7672,7 +6712,6 @@
           <t>React</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr"/>
       <c r="D50" t="n">
         <v>42</v>
       </c>
@@ -7684,7 +6723,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7699,7 +6738,6 @@
           <t>数据挖掘</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr"/>
       <c r="D51" t="n">
         <v>43</v>
       </c>
@@ -7711,7 +6749,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7726,7 +6764,6 @@
           <t>Redis</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr"/>
       <c r="D52" t="n">
         <v>44</v>
       </c>
@@ -7738,7 +6775,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7753,7 +6790,6 @@
           <t>MATLAB</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr"/>
       <c r="D53" t="n">
         <v>45</v>
       </c>
@@ -7765,7 +6801,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7780,7 +6816,6 @@
           <t>Hive</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr"/>
       <c r="D54" t="n">
         <v>46</v>
       </c>
@@ -7792,7 +6827,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7807,7 +6842,6 @@
           <t>PHP</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr"/>
       <c r="D55" t="n">
         <v>47</v>
       </c>
@@ -7819,7 +6853,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7834,7 +6868,6 @@
           <t>Power BI</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr"/>
       <c r="D56" t="n">
         <v>48</v>
       </c>
@@ -7846,7 +6879,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7861,7 +6894,6 @@
           <t>Spark</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
       <c r="D57" t="n">
         <v>49</v>
       </c>
@@ -7873,7 +6905,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7888,7 +6920,6 @@
           <t>强化学习</t>
         </is>
       </c>
-      <c r="C58" t="inlineStr"/>
       <c r="D58" t="n">
         <v>50</v>
       </c>
@@ -7900,7 +6931,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>排名差 = 扩展统计范围排名 − 主统计范围排名（负值表示扩展统计范围中更靠前）</t>
+          <t>排名差 = 扩展口径排名 − 主口径排名（负值表示扩展口径中更靠前）</t>
         </is>
       </c>
     </row>
@@ -7946,7 +6977,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>group = 办公工具，对 intern_id 去重后的岗位数（正式统计范围）</t>
+          <t>group = 办公工具，对 intern_id 去重后的岗位数（正式口径）</t>
         </is>
       </c>
     </row>
@@ -7968,7 +6999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>组内技能岗位数简单相加（错误统计范围）</t>
+          <t>组内技能岗位数简单相加（错误口径）</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -17170,7 +16201,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17217,7 +16248,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17264,7 +16295,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17311,7 +16342,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17358,7 +16389,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17405,7 +16436,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17452,7 +16483,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17499,7 +16530,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17546,7 +16577,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17593,7 +16624,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17640,7 +16671,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17687,7 +16718,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17734,7 +16765,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17781,7 +16812,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17828,7 +16859,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17875,7 +16906,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17922,7 +16953,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -17969,7 +17000,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18016,7 +17047,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18063,7 +17094,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18181,7 +17212,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18228,7 +17259,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18275,7 +17306,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18322,7 +17353,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18369,7 +17400,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18416,7 +17447,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18463,7 +17494,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18510,7 +17541,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18557,7 +17588,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18604,7 +17635,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18651,7 +17682,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18698,7 +17729,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18745,7 +17776,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18792,7 +17823,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18839,7 +17870,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -18957,7 +17988,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19004,7 +18035,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19051,7 +18082,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19098,7 +18129,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19145,7 +18176,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19192,7 +18223,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19239,7 +18270,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19357,7 +18388,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19404,7 +18435,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19451,7 +18482,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19498,7 +18529,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19545,7 +18576,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
@@ -19592,7 +18623,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>REQUIREMENT_SECTION（分母 = 主统计范围岗位数）</t>
+          <t>REQUIREMENT_SECTION（分母 = 主口径岗位数）</t>
         </is>
       </c>
     </row>
